--- a/【エネマネ】【UT_試験項目表】EMS-SW-01_施設検索画面スマホ (facility_search)/【エネマネ】【UT_試験項目表】EMS-SW-01_施設検索画面スマホ_JP.xlsx
+++ b/【エネマネ】【UT_試験項目表】EMS-SW-01_施設検索画面スマホ (facility_search)/【エネマネ】【UT_試験項目表】EMS-SW-01_施設検索画面スマホ_JP.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10212"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C50B28B-72DB-E045-81D0-FF244682A1F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04FB3FFF-BCF7-1F4E-83AF-289C0D4BDBFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="700" windowWidth="38400" windowHeight="21600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="タイトル" sheetId="5" r:id="rId1"/>
@@ -121,16 +121,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>事前条件</t>
-    <rPh sb="0" eb="2">
-      <t>ジゼン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウケン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>入力値</t>
     <rPh sb="0" eb="2">
       <t>ニュウリョク</t>
@@ -565,6 +555,9 @@
   </si>
   <si>
     <t>・画面解像度を「幅1080px×高さ2400px」に設定されたこと。</t>
+  </si>
+  <si>
+    <t>事前条件</t>
   </si>
 </sst>
 </file>
@@ -1631,7 +1624,7 @@
     <row r="17" spans="2:2" ht="34">
       <c r="B17" s="3" t="str">
         <f ca="1">MID(CELL("filename"),SEARCH("[",CELL("filename"))+1, SEARCH("]",CELL("filename"))-SEARCH("[",CELL("filename"))-6)</f>
-        <v>【エネマネ】【UT_試験項目表】EMS-SW-01_施設検索画面スマホ_JP</v>
+        <v>【エネマネ】【UT_試験結果表】EMS-SW-01_施設検索画面スマホ</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1"/>
@@ -1668,7 +1661,7 @@
   <sheetData>
     <row r="1" spans="1:47">
       <c r="A1" s="74" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B1" s="75"/>
       <c r="C1" s="76"/>
@@ -1685,7 +1678,7 @@
       <c r="J1" s="75"/>
       <c r="K1" s="75"/>
       <c r="L1" s="75" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M1" s="75"/>
       <c r="N1" s="75"/>
@@ -1707,25 +1700,25 @@
       <c r="B2" s="75"/>
       <c r="C2" s="76"/>
       <c r="D2" s="57" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" s="58"/>
       <c r="F2" s="58"/>
       <c r="G2" s="59"/>
       <c r="H2" s="80" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I2" s="80"/>
       <c r="J2" s="80"/>
       <c r="K2" s="80"/>
       <c r="L2" s="81" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M2" s="81"/>
       <c r="N2" s="81"/>
       <c r="O2" s="34"/>
       <c r="P2" s="80" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q2" s="80"/>
       <c r="R2" s="80"/>
@@ -1771,7 +1764,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="78"/>
       <c r="D4" s="60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E4" s="61"/>
       <c r="F4" s="61"/>
@@ -1821,16 +1814,16 @@
         <v>7</v>
       </c>
       <c r="B6" s="69" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6" s="70"/>
       <c r="D6" s="71" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E6" s="72"/>
       <c r="F6" s="73"/>
       <c r="G6" s="63" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H6" s="64"/>
       <c r="I6" s="64"/>
@@ -1855,7 +1848,7 @@
       <c r="B7" s="79"/>
       <c r="C7" s="36"/>
       <c r="D7" s="63" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E7" s="64"/>
       <c r="F7" s="64"/>
@@ -1880,12 +1873,12 @@
     </row>
     <row r="8" spans="1:47" ht="13.5" customHeight="1">
       <c r="A8" s="35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B8" s="79"/>
       <c r="C8" s="36"/>
       <c r="D8" s="63" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E8" s="64"/>
       <c r="F8" s="64"/>
@@ -1913,7 +1906,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="52"/>
       <c r="D10" s="52"/>
@@ -1930,21 +1923,21 @@
       <c r="K10" s="85"/>
       <c r="L10" s="85"/>
       <c r="M10" s="87" t="s">
-        <v>13</v>
+        <v>118</v>
       </c>
       <c r="N10" s="87"/>
       <c r="O10" s="87"/>
       <c r="P10" s="87"/>
       <c r="Q10" s="87"/>
       <c r="R10" s="35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S10" s="79"/>
       <c r="T10" s="79"/>
       <c r="U10" s="79"/>
       <c r="V10" s="36"/>
       <c r="W10" s="35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X10" s="79"/>
       <c r="Y10" s="79"/>
@@ -1952,36 +1945,36 @@
       <c r="AA10" s="79"/>
       <c r="AB10" s="36"/>
       <c r="AC10" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AD10" s="51" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE10" s="52"/>
       <c r="AF10" s="53"/>
       <c r="AG10" s="51" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH10" s="52"/>
       <c r="AI10" s="53"/>
       <c r="AJ10" s="35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK10" s="36"/>
       <c r="AL10" s="35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM10" s="36"/>
       <c r="AN10" s="35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO10" s="36"/>
       <c r="AP10" s="35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ10" s="36"/>
       <c r="AR10" s="87" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS10" s="87"/>
       <c r="AT10" s="87"/>
@@ -1989,10 +1982,10 @@
     </row>
     <row r="11" spans="1:47" ht="45.5" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B11" s="66" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" s="67"/>
       <c r="D11" s="67"/>
@@ -2001,7 +1994,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H11" s="30"/>
       <c r="I11" s="30"/>
@@ -2014,14 +2007,14 @@
       <c r="P11" s="30"/>
       <c r="Q11" s="30"/>
       <c r="R11" s="43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S11" s="38"/>
       <c r="T11" s="38"/>
       <c r="U11" s="38"/>
       <c r="V11" s="39"/>
       <c r="W11" s="30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="X11" s="30"/>
       <c r="Y11" s="30"/>
@@ -2050,10 +2043,10 @@
     </row>
     <row r="12" spans="1:47" ht="73" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" s="46"/>
       <c r="D12" s="46"/>
@@ -2062,7 +2055,7 @@
         <v>2</v>
       </c>
       <c r="G12" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H12" s="30"/>
       <c r="I12" s="30"/>
@@ -2070,21 +2063,21 @@
       <c r="K12" s="30"/>
       <c r="L12" s="30"/>
       <c r="M12" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N12" s="30"/>
       <c r="O12" s="30"/>
       <c r="P12" s="30"/>
       <c r="Q12" s="30"/>
       <c r="R12" s="43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S12" s="38"/>
       <c r="T12" s="38"/>
       <c r="U12" s="38"/>
       <c r="V12" s="39"/>
       <c r="W12" s="30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="X12" s="30"/>
       <c r="Y12" s="30"/>
@@ -2113,10 +2106,10 @@
     </row>
     <row r="13" spans="1:47" ht="91" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13" s="49"/>
       <c r="D13" s="49"/>
@@ -2125,7 +2118,7 @@
         <v>3</v>
       </c>
       <c r="G13" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H13" s="30"/>
       <c r="I13" s="30"/>
@@ -2133,21 +2126,21 @@
       <c r="K13" s="30"/>
       <c r="L13" s="30"/>
       <c r="M13" s="30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N13" s="30"/>
       <c r="O13" s="30"/>
       <c r="P13" s="30"/>
       <c r="Q13" s="30"/>
       <c r="R13" s="43" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S13" s="38"/>
       <c r="T13" s="38"/>
       <c r="U13" s="38"/>
       <c r="V13" s="39"/>
       <c r="W13" s="30" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X13" s="44"/>
       <c r="Y13" s="44"/>
@@ -2176,10 +2169,10 @@
     </row>
     <row r="14" spans="1:47" ht="73.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" s="49"/>
       <c r="D14" s="49"/>
@@ -2188,7 +2181,7 @@
         <v>4</v>
       </c>
       <c r="G14" s="30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H14" s="30"/>
       <c r="I14" s="30"/>
@@ -2196,21 +2189,21 @@
       <c r="K14" s="30"/>
       <c r="L14" s="30"/>
       <c r="M14" s="30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N14" s="30"/>
       <c r="O14" s="30"/>
       <c r="P14" s="30"/>
       <c r="Q14" s="30"/>
       <c r="R14" s="43" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S14" s="38"/>
       <c r="T14" s="38"/>
       <c r="U14" s="38"/>
       <c r="V14" s="39"/>
       <c r="W14" s="30" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X14" s="44"/>
       <c r="Y14" s="44"/>
@@ -2239,10 +2232,10 @@
     </row>
     <row r="15" spans="1:47" ht="56" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C15" s="38"/>
       <c r="D15" s="38"/>
@@ -2251,7 +2244,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H15" s="41"/>
       <c r="I15" s="41"/>
@@ -2264,14 +2257,14 @@
       <c r="P15" s="30"/>
       <c r="Q15" s="30"/>
       <c r="R15" s="43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S15" s="38"/>
       <c r="T15" s="38"/>
       <c r="U15" s="38"/>
       <c r="V15" s="39"/>
       <c r="W15" s="30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="X15" s="30"/>
       <c r="Y15" s="30"/>
@@ -2300,10 +2293,10 @@
     </row>
     <row r="16" spans="1:47" ht="56" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C16" s="38"/>
       <c r="D16" s="38"/>
@@ -2312,7 +2305,7 @@
         <v>2</v>
       </c>
       <c r="G16" s="40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H16" s="41"/>
       <c r="I16" s="41"/>
@@ -2320,21 +2313,21 @@
       <c r="K16" s="41"/>
       <c r="L16" s="42"/>
       <c r="M16" s="30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N16" s="30"/>
       <c r="O16" s="30"/>
       <c r="P16" s="30"/>
       <c r="Q16" s="30"/>
       <c r="R16" s="43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S16" s="38"/>
       <c r="T16" s="38"/>
       <c r="U16" s="38"/>
       <c r="V16" s="39"/>
       <c r="W16" s="30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="X16" s="30"/>
       <c r="Y16" s="30"/>
@@ -2363,10 +2356,10 @@
     </row>
     <row r="17" spans="1:47" ht="56" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C17" s="38"/>
       <c r="D17" s="38"/>
@@ -2375,7 +2368,7 @@
         <v>3</v>
       </c>
       <c r="G17" s="40" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H17" s="41"/>
       <c r="I17" s="41"/>
@@ -2383,21 +2376,21 @@
       <c r="K17" s="41"/>
       <c r="L17" s="42"/>
       <c r="M17" s="40" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N17" s="41"/>
       <c r="O17" s="41"/>
       <c r="P17" s="41"/>
       <c r="Q17" s="42"/>
       <c r="R17" s="43" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="S17" s="38"/>
       <c r="T17" s="38"/>
       <c r="U17" s="38"/>
       <c r="V17" s="39"/>
       <c r="W17" s="30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="X17" s="30"/>
       <c r="Y17" s="30"/>
@@ -2426,10 +2419,10 @@
     </row>
     <row r="18" spans="1:47" ht="36.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C18" s="41"/>
       <c r="D18" s="41"/>
@@ -2438,7 +2431,7 @@
         <v>4</v>
       </c>
       <c r="G18" s="40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H18" s="41"/>
       <c r="I18" s="41"/>
@@ -2451,14 +2444,14 @@
       <c r="P18" s="41"/>
       <c r="Q18" s="42"/>
       <c r="R18" s="43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S18" s="38"/>
       <c r="T18" s="38"/>
       <c r="U18" s="38"/>
       <c r="V18" s="39"/>
       <c r="W18" s="30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X18" s="30"/>
       <c r="Y18" s="30"/>
@@ -2487,10 +2480,10 @@
     </row>
     <row r="19" spans="1:47" ht="36.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" s="41"/>
       <c r="D19" s="41"/>
@@ -2499,7 +2492,7 @@
         <v>5</v>
       </c>
       <c r="G19" s="40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H19" s="41"/>
       <c r="I19" s="41"/>
@@ -2507,21 +2500,21 @@
       <c r="K19" s="41"/>
       <c r="L19" s="42"/>
       <c r="M19" s="40" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N19" s="41"/>
       <c r="O19" s="41"/>
       <c r="P19" s="41"/>
       <c r="Q19" s="42"/>
       <c r="R19" s="43" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="S19" s="38"/>
       <c r="T19" s="38"/>
       <c r="U19" s="38"/>
       <c r="V19" s="39"/>
       <c r="W19" s="30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X19" s="30"/>
       <c r="Y19" s="30"/>
@@ -2550,10 +2543,10 @@
     </row>
     <row r="20" spans="1:47" ht="69" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C20" s="38"/>
       <c r="D20" s="38"/>
@@ -2562,7 +2555,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H20" s="38"/>
       <c r="I20" s="38"/>
@@ -2570,21 +2563,21 @@
       <c r="K20" s="38"/>
       <c r="L20" s="39"/>
       <c r="M20" s="30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N20" s="30"/>
       <c r="O20" s="30"/>
       <c r="P20" s="30"/>
       <c r="Q20" s="30"/>
       <c r="R20" s="43" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="S20" s="38"/>
       <c r="T20" s="38"/>
       <c r="U20" s="38"/>
       <c r="V20" s="39"/>
       <c r="W20" s="40" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="X20" s="41"/>
       <c r="Y20" s="41"/>
@@ -2613,10 +2606,10 @@
     </row>
     <row r="21" spans="1:47" s="16" customFormat="1" ht="67.5" customHeight="1">
       <c r="A21" s="28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C21" s="38"/>
       <c r="D21" s="38"/>
@@ -2625,7 +2618,7 @@
         <v>2</v>
       </c>
       <c r="G21" s="44" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H21" s="44"/>
       <c r="I21" s="44"/>
@@ -2633,21 +2626,21 @@
       <c r="K21" s="44"/>
       <c r="L21" s="44"/>
       <c r="M21" s="30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N21" s="30"/>
       <c r="O21" s="30"/>
       <c r="P21" s="30"/>
       <c r="Q21" s="30"/>
       <c r="R21" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="S21" s="38"/>
       <c r="T21" s="38"/>
       <c r="U21" s="38"/>
       <c r="V21" s="39"/>
       <c r="W21" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="X21" s="44"/>
       <c r="Y21" s="44"/>
@@ -2676,10 +2669,10 @@
     </row>
     <row r="22" spans="1:47" s="16" customFormat="1" ht="72" customHeight="1">
       <c r="A22" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B22" s="93" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C22" s="94"/>
       <c r="D22" s="94"/>
@@ -2688,7 +2681,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H22" s="30"/>
       <c r="I22" s="30"/>
@@ -2696,21 +2689,21 @@
       <c r="K22" s="30"/>
       <c r="L22" s="30"/>
       <c r="M22" s="30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N22" s="30"/>
       <c r="O22" s="30"/>
       <c r="P22" s="30"/>
       <c r="Q22" s="30"/>
       <c r="R22" s="43" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="S22" s="38"/>
       <c r="T22" s="38"/>
       <c r="U22" s="38"/>
       <c r="V22" s="39"/>
       <c r="W22" s="30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="X22" s="30"/>
       <c r="Y22" s="30"/>
@@ -2739,10 +2732,10 @@
     </row>
     <row r="23" spans="1:47" ht="68.5" customHeight="1">
       <c r="A23" s="29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C23" s="38"/>
       <c r="D23" s="38"/>
@@ -2751,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="G23" s="30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H23" s="30"/>
       <c r="I23" s="30"/>
@@ -2759,21 +2752,21 @@
       <c r="K23" s="44"/>
       <c r="L23" s="44"/>
       <c r="M23" s="30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N23" s="30"/>
       <c r="O23" s="30"/>
       <c r="P23" s="30"/>
       <c r="Q23" s="30"/>
       <c r="R23" s="43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S23" s="38"/>
       <c r="T23" s="38"/>
       <c r="U23" s="38"/>
       <c r="V23" s="39"/>
       <c r="W23" s="30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="X23" s="44"/>
       <c r="Y23" s="44"/>
@@ -3023,7 +3016,7 @@
   <sheetData>
     <row r="2" spans="1:6">
       <c r="A2" s="101" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" s="101"/>
     </row>
@@ -3031,27 +3024,27 @@
       <c r="A3" s="101"/>
       <c r="B3" s="101"/>
       <c r="C3" s="102" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D3" s="103"/>
       <c r="E3" s="102" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F3" s="103"/>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1">
       <c r="A4" s="104" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="106" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="106" t="s">
-        <v>64</v>
-      </c>
       <c r="C4" s="108" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D4" s="108"/>
       <c r="E4" s="108" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F4" s="108"/>
     </row>
@@ -3059,16 +3052,16 @@
       <c r="A5" s="105"/>
       <c r="B5" s="107"/>
       <c r="C5" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="21" t="s">
-        <v>66</v>
-      </c>
       <c r="E5" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="21" t="s">
         <v>65</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3076,19 +3069,19 @@
         <v>1</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C6" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="24" t="s">
-        <v>68</v>
-      </c>
       <c r="E6" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" s="24" t="s">
         <v>67</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3096,19 +3089,19 @@
         <v>2</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C7" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="24" t="s">
         <v>67</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3116,19 +3109,19 @@
         <v>3</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C8" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="24" t="s">
         <v>67</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3136,19 +3129,19 @@
         <v>4</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="24" t="s">
         <v>67</v>
-      </c>
-      <c r="F9" s="24" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3156,74 +3149,74 @@
         <v>5</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="109" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B12" s="109"/>
       <c r="C12" s="109"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B13" s="99" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C13" s="100"/>
       <c r="D13" s="25"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="99" t="s">
         <v>73</v>
-      </c>
-      <c r="B14" s="99" t="s">
-        <v>74</v>
       </c>
       <c r="C14" s="100"/>
       <c r="D14" s="25"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B15" s="110" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" s="111"/>
       <c r="D15" s="26"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B16" s="99" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C16" s="100"/>
       <c r="D16" s="25"/>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B17" s="99" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C17" s="100"/>
     </row>
